--- a/ASG_CAD_MASTER_STANDARD/06_Layer_Register/ASG_Layer_Register.xlsx
+++ b/ASG_CAD_MASTER_STANDARD/06_Layer_Register/ASG_Layer_Register.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colour Logic" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Layer Register'!$A$4:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Layer Register'!$A$4:$L$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,11 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -84,10 +89,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,10 +102,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,20 +471,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,1941 +496,2116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SAEED AL SIRAJ GLASS &amp; ALUMINIUM WORKS L.L.C. | AL SIRAJ GROUP | Standard R0 | 10.10.2026</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SAEED AL SIRAJ GLASS &amp; ALUMINIUM WORKS L.L.C. | AL SIRAJ GROUP | Standard R1 | 10.10.2026 | Generated from asg_standard.py - do not edit, change the source and rebuild</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Layer code</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Full layer name</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Functional group</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ACI colour</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Linetype</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Lineweight (mm)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Lineweight class</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Plot status</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Recommended use</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>G01</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ASG-OUTLINE-PRIMARY</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Primary visible outlines</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Primary visible outlines; ACI 7, Continuous, 0.35 mm</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Overall frame / panel outlines in elevation and plan</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Primary visible outlines. ACI 7, Continuous, 0.35 mm</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Overall frame / panel / opening outlines in elevation and plan</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>G02</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ASG-OUTLINE-SECONDARY</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Secondary visible lines</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Secondary visible lines; ACI 8, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Secondary visible lines. ACI 8, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Edges beyond, minor returns, internal lines</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>G03</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ASG-ALUMINIUM-PROFILE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Aluminium profiles</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Aluminium profiles; ACI 7, Continuous, 0.25 mm</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Aluminium profiles. ACI 7, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Frames, mullions, transoms, sashes, beads (elevation and section)</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>G04</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ASG-GLASS</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Glass and mirror</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Glass and mirror; ACI 4, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Glass / mirror edges, DGU / laminate interlayer lines</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Glass and mirror. ACI 4, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Glass / mirror edges, DGU and laminate ply lines</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>G05</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ASG-STAINLESS-STEEL</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Stainless steel</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Stainless steel; ACI 7, Continuous, 0.25 mm</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Stainless steel. ACI 7, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>SS fittings, spigots, channels, handrails, patch plates</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>G06</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ASG-MILD-STEEL</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Mild steel</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Mild steel; ACI 7, Continuous, 0.30 mm</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Mild steel. ACI 7, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>MS brackets, sub-frames, support steel, base plates</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>G07</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ASG-HARDWARE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Hardware; ACI 8, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware. ACI 8, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Hinges, handles, locks, rollers, closers, patch fittings</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>G08</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ASG-FIXING</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Fixings</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Fixings; ACI 8, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Fixings. ACI 8, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Anchors, screws, bolts, rivets, fixing brackets</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>G09</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>ASG-GASKET</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Gaskets</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Gaskets; ACI 8, Continuous, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Gaskets. ACI 8, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>EPDM gaskets, brushes, setting / distance blocks</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>G10</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ASG-SEALANT</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Sealants</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Sealants; ACI 8, Continuous, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Sealants. ACI 8, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Structural / weather silicone, backer rod, tapes</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>G11</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>ASG-INSULATION</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Insulation</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Insulation; ACI 252, Continuous, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Insulation. ACI 252, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Insulation and thermal breaks (plots grey)</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>G12</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>ASG-CLADDING</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Cladding</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Cladding; ACI 7, Continuous, 0.25 mm</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Cladding. ACI 7, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>ACP / solid panels, flashings, copings</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>T01</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ASG-HIDDEN</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Hidden geometry</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>HIDDEN2</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hidden geometry; ACI 8, HIDDEN2, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Hidden geometry. ACI 8, HIDDEN2, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Concealed edges, embedded parts</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>T02</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>ASG-CENTERLINE</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Centrelines</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>CENTER2</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Centrelines; ACI 8, CENTER2, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Centrelines. ACI 8, CENTER2, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Axes of symmetry, hole centres, module lines</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>T03</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>ASG-CUTTING-PLANE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Cutting planes</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>PHANTOM2</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Cutting planes; ACI 7, PHANTOM2, 0.35 mm</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Section cut lines (markers go on ASG-SYMBOL)</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Cutting planes. ACI 7, PHANTOM2, 0.35 mm</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Section cut lines (section markers go on ASG-SYMBOL)</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>T04</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>ASG-SECTION-CUT</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Section cut outlines</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Extra heavy</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Section cut outlines; ACI 7, Continuous, 0.40 mm</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Section cut outlines. ACI 7, Continuous, 0.50 mm</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Outline of material cut by the section plane - heaviest geometry</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>T05</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>ASG-HATCH</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Section hatching</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Hatch</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Section hatching; ACI 252, Continuous, 0.09 mm</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Section hatching. ACI 252, Continuous, 0.09 mm</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Pattern hatches in sections (plots grey)</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>T06</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>ASG-HATCH-FILL</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Solid fills</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>251</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Hatch</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Solid fills; ACI 251, Continuous, 0.09 mm</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Solid fills. ACI 251, Continuous, 0.09 mm</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Solid fill of thin aluminium / steel walls (plots dark grey)</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>T07</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>ASG-SETOUT</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Setting-out geometry (plotted)</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>DASHDOT2</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Setting-out geometry (plotted); ACI 8, DASHDOT2, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Setting-out geometry (plotted). ACI 8, DASHDOT2, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Opening lines, setting-out lines that must print</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>T08</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>ASG-REFERENCE</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Reference geometry</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>253</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Reference geometry; ACI 253, Continuous, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Reference geometry. ACI 253, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Architectural / structural background, xrefs (plots light grey)</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>T09</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>ASG-CONSTRUCTION</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Construction geometry (NOT plotted)</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Non-plot</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>NO PLOT</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Construction geometry (NOT plotted); ACI 6, Continuous, 0.05 mm</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Construction geometry (NOT plotted). ACI 6, Continuous, 0.00 mm</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Temporary helper lines only - never final geometry</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>ASG-DIMENSION</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Dimensions</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Dimensions; ACI 3, Continuous, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Dimensions. ACI 3, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>All dimensions</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>ASG-TEXT</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>General text</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>General text; ACI 7, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>General text. ACI 7, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Labels, view titles</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>ASG-TEXT-NOTE</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Notes; ACI 7, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Notes. ACI 7, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>General and specification notes</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>ASG-MULTILEADER</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Multileaders</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Multileaders; ACI 3, Continuous, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Multileaders. ACI 3, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Callouts and material labels</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ASG-TABLE</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Tables</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Light</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Tables; ACI 7, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Tables. ACI 7, Continuous, 0.18 mm</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Schedules, registers, note tables</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ASG-LEVEL</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Levels</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Levels; ACI 3, Continuous, 0.18 mm</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Levels. ACI 3, Continuous, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>FFL / SSL / sill / head level markers</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>A07</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>ASG-GRID</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Grids</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>CENTER</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Fine</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Grids; ACI 8, CENTER, 0.13 mm</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Grids. ACI 8, CENTER, 0.13 mm</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Structural / architectural grid lines and bubbles</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>A08</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ASG-REVISION</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Revision clouds</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Revision clouds; ACI 1, Continuous, 0.25 mm</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Revision clouds. ACI 1, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Revision clouds and delta tags</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>A09</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>ASG-SYMBOL</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Drafting symbols</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Drafting symbols; ACI 3, Continuous, 0.25 mm</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Drafting symbols. ACI 3, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Section / detail / elevation marks, north arrow</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>ASG-BORDER</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Sheet borders</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Extra heavy</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Sheet borders; ACI 7, Continuous, 0.50 mm</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Sheet borders. ACI 7, Continuous, 0.50 mm</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Border frame in layouts</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>ASG-TITLEBLOCK</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Title blocks</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Plot</t>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Title blocks; ACI 7, Continuous, 0.25 mm</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Title blocks. ACI 7, Continuous, 0.25 mm</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Title block insert and attributes</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>ASG-VIEWPORT</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Viewports (NOT plotted)</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Non-plot</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>NO PLOT</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Viewports (NOT plotted); ACI 6, Continuous, 0.00 mm</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Viewports (NOT plotted). ACI 6, Continuous, 0.00 mm</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>All layout viewports</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>ASG-NOPLOT</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Non-plot objects</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Non-plot</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>NO PLOT</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Non-plot objects; ACI 6, Continuous, 0.00 mm</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Internal markups, reminders - never printed</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>R0</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Non-plot objects. ACI 6, Continuous, 0.00 mm</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Internal markups and reminders - never printed</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K38"/>
+  <autoFilter ref="A4:L38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2434,25 +2616,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Lineweight (mm)</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Layers</t>
         </is>
@@ -2466,129 +2655,125 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sheet border</t>
+          <t>Extra heavy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASG-BORDER</t>
+          <t>Section cut outlines, sheet border</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ASG-SECTION-CUT, ASG-BORDER</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Section cut outline</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ASG-SECTION-CUT</t>
+          <t>Primary visible outlines, cutting planes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ASG-OUTLINE-PRIMARY, ASG-CUTTING-PLANE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Primary outline, cutting plane</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASG-OUTLINE-PRIMARY, ASG-CUTTING-PLANE</t>
+          <t>Aluminium, steel, cladding, symbols, revisions, title block</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ASG-ALUMINIUM-PROFILE, ASG-STAINLESS-STEEL, ASG-MILD-STEEL, ASG-CLADDING, ASG-REVISION, ASG-SYMBOL, ASG-TITLEBLOCK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ASG-MILD-STEEL</t>
+          <t>Secondary lines, glass, hardware, fixings, hidden lines, text, tables</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ASG-OUTLINE-SECONDARY, ASG-GLASS, ASG-HARDWARE, ASG-FIXING, ASG-HIDDEN, ASG-TEXT, ASG-TEXT-NOTE, ASG-TABLE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aluminium, stainless, cladding, symbols, title block, revision</t>
+          <t>Fine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASG-ALUMINIUM-PROFILE, ASG-STAINLESS-STEEL, ASG-CLADDING, ASG-REVISION, ASG-SYMBOL, ASG-TITLEBLOCK</t>
+          <t>Dimensions, leaders, centrelines, grids, seals, insulation, set-out, reference</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ASG-GASKET, ASG-SEALANT, ASG-INSULATION, ASG-CENTERLINE, ASG-SETOUT, ASG-REFERENCE, ASG-DIMENSION, ASG-MULTILEADER, ASG-LEVEL, ASG-GRID</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Secondary lines, glass, hardware, fixings, hidden, text</t>
+          <t>Hatch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASG-OUTLINE-SECONDARY, ASG-GLASS, ASG-HARDWARE, ASG-FIXING, ASG-HIDDEN, ASG-TEXT, ASG-TEXT-NOTE, ASG-TABLE, ASG-LEVEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dimensions, leaders, centrelines, seals, insulation, set-out, reference</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ASG-GASKET, ASG-SEALANT, ASG-INSULATION, ASG-CENTERLINE, ASG-SETOUT, ASG-REFERENCE, ASG-DIMENSION, ASG-MULTILEADER, ASG-GRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Hatches and fills</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+          <t>Hatch patterns and fills only (also plotted grey)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>ASG-HATCH, ASG-HATCH-FILL</t>
         </is>
@@ -2605,27 +2790,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ACI</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Plotted (ASG_Monochrome.ctb)</t>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Plotted with ASG_Monochrome.ctb</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2840,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Secondary geometry, hardware, seals, hidden, centre, grids</t>
+          <t>Secondary geometry, hardware, seals, hidden, centrelines, grids</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Black (thinner weights)</t>
+          <t>Black (lighter weights)</t>
         </is>
       </c>
     </row>
@@ -2734,17 +2920,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>251 / 252 / 253</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fills / hatch &amp; insulation / reference</t>
+          <t>Solid fills (aluminium / steel walls in section)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grey 36% / 52% / 68% darkness</t>
+          <t>Grey RGB 91 (about 64 % dark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hatch patterns, insulation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grey RGB 132 (about 48 % dark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reference background / xrefs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grey RGB 173 (about 32 % dark)</t>
         </is>
       </c>
     </row>
